--- a/public/inputs/y03-physical-education - input.xlsx
+++ b/public/inputs/y03-physical-education - input.xlsx
@@ -444,7 +444,6 @@
           <t>Unit 1 · Moving Well</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -457,7 +456,6 @@
           <t>1.1 Practise and refine basic movement skills.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -470,7 +468,6 @@
           <t>1.2 Perform movement skills with increasing proficiency and use them sequentially.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -483,7 +480,6 @@
           <t>1.3 Move with control and coordination, using space in different ways and moving with different speeds and dynamics.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -496,7 +492,6 @@
           <t>1.4 Refine and extend movement competence and confidence through responding and adapting to the demands of a range of contexts, apparatus and equipment, showing coordination and control.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -509,7 +504,6 @@
           <t>Unit 2 · Understanding Movement</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,7 +516,6 @@
           <t>2.1 Describe own and others’ movements using simple activity-specific vocabulary.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -535,7 +528,6 @@
           <t>2.2 Describe actions, dynamics, space and relationships when observing and engaging in movement.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -548,7 +540,6 @@
           <t>2.3 Use simple criteria to evaluate success and identify the need for improvement in basic movement tasks and challenges.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -561,7 +552,6 @@
           <t>2.4 Understand and follow simple rules, and understand and use tactics and compositional ideas.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -574,7 +564,6 @@
           <t>Unit 3 · Moving Creatively</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -587,7 +576,6 @@
           <t>3.1 Explore a variety of movements and movement patterns that begin to demonstrate creativity.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -597,10 +585,9 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3.2 Explore and discover ways of interacting in movement with different situations and contexts,including a range of apparatus and equipment.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>3.2 Explore and discover ways of interacting in movement with different situations and contexts, including a range of apparatus and equipment.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -613,7 +600,6 @@
           <t>3.3 Respond to given and selected tasks and challenges in a range of movement contexts.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -626,7 +612,6 @@
           <t>3.4 Discover and use a range of compositional ideas to express themes, moods and emotions.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -639,7 +624,6 @@
           <t>Unit 4 · Taking Part</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -652,7 +636,6 @@
           <t>4.1 Show involvement when working alone, when sharing space, inwhole group physical activity and when playing with others.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -665,7 +648,6 @@
           <t>4.2 Know their roles and start to recognise others' roles in a range of simple individual and small team/group context.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -678,7 +660,6 @@
           <t>4.3 Know how to work independently towards the achievement of agreed movements goals.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -691,7 +672,6 @@
           <t>4.4 Begin to take and share the lead in team/group.</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -704,7 +684,6 @@
           <t>4.5 Recognise movement qualities in self and others and be able to describe own movement strengths and areas for improvement.</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -717,7 +696,6 @@
           <t>4.6 Listen to others and respond appropriately in a range of movement tasks and challenges.</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -730,7 +708,6 @@
           <t>Unit 5 · Taking Responsibility</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -743,7 +720,6 @@
           <t>5.1 Show increasing ability to share space and equipment, to take turns and to cooperate with others.</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -756,7 +732,6 @@
           <t>5.2 Understand individual responsibility for moving and using equipment and space safely, following associated rules and regulations</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -769,7 +744,6 @@
           <t>5.3 Demonstrate collaboration and begin to understand what fair play is in team/group physical activities.</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -782,7 +756,6 @@
           <t>5.4 Understand when and how to engage the help of others during group movement tasks.</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -795,7 +768,6 @@
           <t>5.5 Give supportive feedback in partner/small group activities. Show appreciation of and respect for contributions and motivation to improve.</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -808,7 +780,6 @@
           <t>Unit 6 · Healthy Bodies</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -821,7 +792,6 @@
           <t>6.1 Demonstrate understanding of bodily changes during physical activity and the positive benefits of physical activity for health and wellbeing.</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -834,7 +804,6 @@
           <t>6.2 Identify and name which body parts are being used during physical activity and why these are important.</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -847,7 +816,6 @@
           <t>6.3 Identify the required level of intensity during a range of simple physical activities and begin to work towards achieving this.</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -860,7 +828,6 @@
           <t>6.4 Recognise the current limits of own capacities, and understand the risks associated with different contexts and physical activities.</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -873,7 +840,6 @@
           <t>6.5 Understand the importance of warming up and cooling down the body when participating in physical activity</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -886,7 +852,6 @@
           <t>6.6 Understand some components of a healthy diet.</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -896,10 +861,9 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Test term1, term 2 and term 3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Test term 1, term 2 and term 3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
